--- a/documentacao/Testes/Caso de Teste/UC21 -AREA DE TRABALHO - CLINICA.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC21 -AREA DE TRABALHO - CLINICA.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">Observações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status de teste v2 (OK/NOK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observações </t>
   </si>
   <si>
     <r>
@@ -245,6 +251,9 @@
   </si>
   <si>
     <t xml:space="preserve">redirecionamento para o “pacientes” não funciona.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“redirecionamento para o pacientes” não funciona</t>
   </si>
   <si>
     <r>
@@ -408,7 +417,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -462,6 +471,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -519,7 +534,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -552,6 +567,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -560,15 +591,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -644,13 +675,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.22"/>
@@ -683,249 +820,291 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="G7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="67.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="F12" s="12"/>
       <c r="G12" s="6"/>
+      <c r="H12" s="11" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
+      <c r="A13" s="13"/>
       <c r="C13" s="6"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
+      <c r="A14" s="13"/>
       <c r="C14" s="6"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="14"/>
       <c r="G14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
+      <c r="A15" s="13"/>
       <c r="C15" s="6"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="14"/>
       <c r="G15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
+      <c r="A16" s="13"/>
       <c r="C16" s="6"/>
-      <c r="E16" s="10"/>
+      <c r="E16" s="14"/>
       <c r="G16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="G17" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
